--- a/artfynd/A 59128-2020 artfynd.xlsx
+++ b/artfynd/A 59128-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127331336</v>
       </c>
       <c r="B2" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127331321</v>
       </c>
       <c r="B3" t="n">
-        <v>41361</v>
+        <v>41365</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 59128-2020 artfynd.xlsx
+++ b/artfynd/A 59128-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127331336</v>
       </c>
       <c r="B2" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127331321</v>
       </c>
       <c r="B3" t="n">
-        <v>41365</v>
+        <v>41367</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 59128-2020 artfynd.xlsx
+++ b/artfynd/A 59128-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127331336</v>
       </c>
       <c r="B2" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127331321</v>
       </c>
       <c r="B3" t="n">
-        <v>41367</v>
+        <v>41368</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 59128-2020 artfynd.xlsx
+++ b/artfynd/A 59128-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127331336</v>
       </c>
       <c r="B2" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
